--- a/Du_Lieu_Mau_He_Thong/Theo_Phan_He/Ty_Gia_Ngoai_Te/ty_gia_ngoai_te_ngay_26_09_2026.xlsx
+++ b/Du_Lieu_Mau_He_Thong/Theo_Phan_He/Ty_Gia_Ngoai_Te/ty_gia_ngoai_te_ngay_26_09_2026.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ExchangeRates" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TyGiaNgoaiTe" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -33,10 +33,10 @@
     </font>
     <font>
       <name val="Calibri"/>
-      <sz val="10"/>
+      <sz val="10.5"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -47,6 +47,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="0000843D"/>
         <bgColor rgb="0000843D"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F4F9F5"/>
+        <bgColor rgb="00F4F9F5"/>
       </patternFill>
     </fill>
   </fills>
@@ -76,15 +82,21 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
@@ -455,41 +467,41 @@
   <dimension ref="A1:E12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="17" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="21" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26" customHeight="1">
+    <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>currencyCode</t>
+          <t>Mã ngoại tệ</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>buyRate</t>
+          <t>Giá mua tiền mặt (VND)</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>sellRate</t>
+          <t>Giá bán ra (VND)</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>transferRate</t>
+          <t>Giá chuyển khoản (VND)</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>effectiveDate</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
+          <t>Ngày hiệu lực</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="24" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
           <t>USD</t>
@@ -510,28 +522,28 @@
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+    <row r="3" ht="24" customHeight="1">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
       </c>
-      <c r="B3" s="3" t="n">
+      <c r="B3" s="5" t="n">
         <v>26800</v>
       </c>
-      <c r="C3" s="3" t="n">
+      <c r="C3" s="5" t="n">
         <v>28280</v>
       </c>
-      <c r="D3" s="3" t="n">
+      <c r="D3" s="5" t="n">
         <v>27080</v>
       </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-26</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="24" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
           <t>GBP</t>
@@ -552,41 +564,41 @@
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+    <row r="5" ht="24" customHeight="1">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>JPY</t>
         </is>
       </c>
-      <c r="B5" s="3" t="n">
-        <v>162.1</v>
-      </c>
-      <c r="C5" s="3" t="n">
-        <v>171.8</v>
-      </c>
-      <c r="D5" s="3" t="n">
-        <v>163.9</v>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-26</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
+      <c r="B5" s="5" t="n">
+        <v>162.5</v>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>172.1</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>164.2</v>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="24" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
           <t>SGD</t>
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>18880</v>
+        <v>18920</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>19680</v>
+        <v>19720</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>19070</v>
+        <v>19110</v>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
@@ -594,41 +606,41 @@
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+    <row r="7" ht="24" customHeight="1">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>AUD</t>
         </is>
       </c>
-      <c r="B7" s="3" t="n">
-        <v>16410</v>
-      </c>
-      <c r="C7" s="3" t="n">
-        <v>17110</v>
-      </c>
-      <c r="D7" s="3" t="n">
-        <v>16580</v>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-26</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
+      <c r="B7" s="5" t="n">
+        <v>16450</v>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>17150</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>16620</v>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="24" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
           <t>CAD</t>
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>18090</v>
+        <v>18120</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>18850</v>
+        <v>18890</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>18260</v>
+        <v>18300</v>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
@@ -636,41 +648,41 @@
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+    <row r="9" ht="24" customHeight="1">
+      <c r="A9" s="4" t="inlineStr">
         <is>
           <t>CHF</t>
         </is>
       </c>
-      <c r="B9" s="3" t="n">
-        <v>28710</v>
-      </c>
-      <c r="C9" s="3" t="n">
-        <v>29920</v>
-      </c>
-      <c r="D9" s="3" t="n">
-        <v>29000</v>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-26</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
+      <c r="B9" s="5" t="n">
+        <v>28750</v>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>29970</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>29040</v>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="24" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
           <t>CNY</t>
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>3470</v>
+        <v>3480</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>3620</v>
+        <v>3630</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>3505</v>
+        <v>3515</v>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
@@ -678,41 +690,41 @@
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
+    <row r="11" ht="24" customHeight="1">
+      <c r="A11" s="4" t="inlineStr">
         <is>
           <t>KRW</t>
         </is>
       </c>
-      <c r="B11" s="3" t="n">
-        <v>18.1</v>
-      </c>
-      <c r="C11" s="3" t="n">
-        <v>20.12</v>
-      </c>
-      <c r="D11" s="3" t="n">
-        <v>19.2</v>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-26</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
+      <c r="B11" s="5" t="n">
+        <v>18.15</v>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>20.18</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>19.25</v>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="24" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
         <is>
           <t>THB</t>
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>712</v>
+        <v>715</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>745</v>
+        <v>748</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>726</v>
+        <v>729</v>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
